--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133624512</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133614931</v>
       </c>
       <c r="B3" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>133614917</v>
       </c>
       <c r="B4" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
         <v>133616224</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>133624485</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>133613993</v>
       </c>
       <c r="B8" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>133614003</v>
       </c>
       <c r="B9" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>133624458</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>133624561</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133616224</v>
+        <v>133624485</v>
       </c>
       <c r="B6" t="n">
         <v>79334</v>
@@ -1136,19 +1136,22 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471303</v>
+        <v>471484</v>
       </c>
       <c r="R6" t="n">
-        <v>6796981</v>
+        <v>6797049</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,19 +1178,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt på vissa tallar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,25 +1194,26 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133624485</v>
+        <v>133616224</v>
       </c>
       <c r="B7" t="n">
         <v>79334</v>
@@ -1243,22 +1242,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Djupån, Djupån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471484</v>
+        <v>471303</v>
       </c>
       <c r="R7" t="n">
-        <v>6797049</v>
+        <v>6796981</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,14 +1281,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt på vissa tallar</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,19 +1302,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133614003</v>
+        <v>133624458</v>
       </c>
       <c r="B9" t="n">
-        <v>79092</v>
+        <v>79334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,37 +1438,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammyren, Dammyren, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471474</v>
+        <v>471511</v>
       </c>
       <c r="R9" t="n">
-        <v>6797013</v>
+        <v>6796820</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,19 +1498,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:59</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,25 +1514,26 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133624458</v>
+        <v>133624561</v>
       </c>
       <c r="B10" t="n">
         <v>79334</v>
@@ -1572,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471511</v>
+        <v>471400</v>
       </c>
       <c r="R10" t="n">
-        <v>6796820</v>
+        <v>6797197</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1612,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Måttligt på tallar</t>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133624561</v>
+        <v>133614003</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>79092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,40 +1650,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471400</v>
+        <v>471474</v>
       </c>
       <c r="R11" t="n">
-        <v>6797197</v>
+        <v>6797013</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1711,14 +1707,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sparsamt på vissa tallar</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,19 +1728,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133624458</v>
+        <v>133614003</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>79092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,40 +1438,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471511</v>
+        <v>471474</v>
       </c>
       <c r="R9" t="n">
-        <v>6796820</v>
+        <v>6797013</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,14 +1495,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Måttligt på tallar</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,26 +1516,25 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133624561</v>
+        <v>133624458</v>
       </c>
       <c r="B10" t="n">
         <v>79334</v>
@@ -1571,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471400</v>
+        <v>471511</v>
       </c>
       <c r="R10" t="n">
-        <v>6797197</v>
+        <v>6796820</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1611,7 +1612,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt på vissa tallar</t>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133614003</v>
+        <v>133624561</v>
       </c>
       <c r="B11" t="n">
-        <v>79092</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,37 +1651,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammyren, Dammyren, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471474</v>
+        <v>471400</v>
       </c>
       <c r="R11" t="n">
-        <v>6797013</v>
+        <v>6797197</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,19 +1711,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:59</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,18 +1727,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -1100,14 +1100,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133624485</v>
+        <v>133616224</v>
       </c>
       <c r="B6" t="n">
         <v>79334</v>
@@ -1136,22 +1136,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Djupån, Djupån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471484</v>
+        <v>471303</v>
       </c>
       <c r="R6" t="n">
-        <v>6797049</v>
+        <v>6796981</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,14 +1175,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt på vissa tallar</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,26 +1196,25 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133616224</v>
+        <v>133624485</v>
       </c>
       <c r="B7" t="n">
         <v>79334</v>
@@ -1242,19 +1243,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471303</v>
+        <v>471484</v>
       </c>
       <c r="R7" t="n">
-        <v>6796981</v>
+        <v>6797049</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,19 +1285,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt på vissa tallar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,18 +1301,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133614003</v>
+        <v>133624458</v>
       </c>
       <c r="B9" t="n">
-        <v>79092</v>
+        <v>79334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,37 +1438,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammyren, Dammyren, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471474</v>
+        <v>471511</v>
       </c>
       <c r="R9" t="n">
-        <v>6797013</v>
+        <v>6796820</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,19 +1498,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:59</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,25 +1514,26 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133624458</v>
+        <v>133624561</v>
       </c>
       <c r="B10" t="n">
         <v>79334</v>
@@ -1572,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471511</v>
+        <v>471400</v>
       </c>
       <c r="R10" t="n">
-        <v>6796820</v>
+        <v>6797197</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1612,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Måttligt på tallar</t>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133624561</v>
+        <v>133614003</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>79092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,40 +1650,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471400</v>
+        <v>471474</v>
       </c>
       <c r="R11" t="n">
-        <v>6797197</v>
+        <v>6797013</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1711,14 +1707,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sparsamt på vissa tallar</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,19 +1728,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133624512</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133614931</v>
       </c>
       <c r="B3" t="n">
-        <v>79092</v>
+        <v>79106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>133614917</v>
       </c>
       <c r="B4" t="n">
-        <v>78341</v>
+        <v>78352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>133615990</v>
       </c>
       <c r="B5" t="n">
-        <v>5179</v>
+        <v>5181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>133616224</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>133624485</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>133613993</v>
       </c>
       <c r="B8" t="n">
-        <v>79091</v>
+        <v>79105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>133624458</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>133624561</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>133614003</v>
       </c>
       <c r="B11" t="n">
-        <v>79092</v>
+        <v>79106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133616224</v>
+        <v>133624485</v>
       </c>
       <c r="B6" t="n">
         <v>79348</v>
@@ -1136,19 +1136,22 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471303</v>
+        <v>471484</v>
       </c>
       <c r="R6" t="n">
-        <v>6796981</v>
+        <v>6797049</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,19 +1178,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt på vissa tallar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,25 +1194,26 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133624485</v>
+        <v>133616224</v>
       </c>
       <c r="B7" t="n">
         <v>79348</v>
@@ -1243,22 +1242,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Djupån, Djupån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471484</v>
+        <v>471303</v>
       </c>
       <c r="R7" t="n">
-        <v>6797049</v>
+        <v>6796981</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,14 +1281,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt på vissa tallar</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,19 +1302,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133624458</v>
+        <v>133614003</v>
       </c>
       <c r="B9" t="n">
-        <v>79348</v>
+        <v>79106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,40 +1438,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471511</v>
+        <v>471474</v>
       </c>
       <c r="R9" t="n">
-        <v>6796820</v>
+        <v>6797013</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,14 +1495,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Måttligt på tallar</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,26 +1516,25 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133624561</v>
+        <v>133624458</v>
       </c>
       <c r="B10" t="n">
         <v>79348</v>
@@ -1571,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471400</v>
+        <v>471511</v>
       </c>
       <c r="R10" t="n">
-        <v>6797197</v>
+        <v>6796820</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1611,7 +1612,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt på vissa tallar</t>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133614003</v>
+        <v>133624561</v>
       </c>
       <c r="B11" t="n">
-        <v>79106</v>
+        <v>79348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,37 +1651,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammyren, Dammyren, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471474</v>
+        <v>471400</v>
       </c>
       <c r="R11" t="n">
-        <v>6797013</v>
+        <v>6797197</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,19 +1711,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:59</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,18 +1727,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133624512</v>
       </c>
       <c r="B2" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133614931</v>
       </c>
       <c r="B3" t="n">
-        <v>79106</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>133614917</v>
       </c>
       <c r="B4" t="n">
-        <v>78352</v>
+        <v>78362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>133624485</v>
       </c>
       <c r="B6" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>133616224</v>
       </c>
       <c r="B7" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>133613993</v>
       </c>
       <c r="B8" t="n">
-        <v>79105</v>
+        <v>79115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133614003</v>
+        <v>133624458</v>
       </c>
       <c r="B9" t="n">
-        <v>79106</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,37 +1438,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammyren, Dammyren, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471474</v>
+        <v>471511</v>
       </c>
       <c r="R9" t="n">
-        <v>6797013</v>
+        <v>6796820</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,19 +1498,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:59</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,28 +1514,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133624458</v>
+        <v>133624561</v>
       </c>
       <c r="B10" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471511</v>
+        <v>471400</v>
       </c>
       <c r="R10" t="n">
-        <v>6796820</v>
+        <v>6797197</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1612,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Måttligt på tallar</t>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133624561</v>
+        <v>133614003</v>
       </c>
       <c r="B11" t="n">
-        <v>79348</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,40 +1650,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471400</v>
+        <v>471474</v>
       </c>
       <c r="R11" t="n">
-        <v>6797197</v>
+        <v>6797013</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1711,14 +1707,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sparsamt på vissa tallar</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,19 +1728,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133624485</v>
+        <v>133616224</v>
       </c>
       <c r="B6" t="n">
         <v>79358</v>
@@ -1136,22 +1136,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Djupån, Djupån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471484</v>
+        <v>471303</v>
       </c>
       <c r="R6" t="n">
-        <v>6797049</v>
+        <v>6796981</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,14 +1175,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt på vissa tallar</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,26 +1196,25 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133616224</v>
+        <v>133624485</v>
       </c>
       <c r="B7" t="n">
         <v>79358</v>
@@ -1242,19 +1243,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471303</v>
+        <v>471484</v>
       </c>
       <c r="R7" t="n">
-        <v>6796981</v>
+        <v>6797049</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,19 +1285,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt på vissa tallar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,18 +1301,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133624458</v>
+        <v>133614003</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,40 +1438,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471511</v>
+        <v>471474</v>
       </c>
       <c r="R9" t="n">
-        <v>6796820</v>
+        <v>6797013</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,14 +1495,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Måttligt på tallar</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,26 +1516,25 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133624561</v>
+        <v>133624458</v>
       </c>
       <c r="B10" t="n">
         <v>79358</v>
@@ -1571,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471400</v>
+        <v>471511</v>
       </c>
       <c r="R10" t="n">
-        <v>6797197</v>
+        <v>6796820</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1611,7 +1612,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt på vissa tallar</t>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133614003</v>
+        <v>133624561</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,37 +1651,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammyren, Dammyren, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471474</v>
+        <v>471400</v>
       </c>
       <c r="R11" t="n">
-        <v>6797013</v>
+        <v>6797197</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,19 +1711,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:59</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,18 +1727,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133614003</v>
+        <v>133624458</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,37 +1438,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammyren, Dammyren, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471474</v>
+        <v>471511</v>
       </c>
       <c r="R9" t="n">
-        <v>6797013</v>
+        <v>6796820</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,19 +1498,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:59</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,25 +1514,26 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133624458</v>
+        <v>133624561</v>
       </c>
       <c r="B10" t="n">
         <v>79358</v>
@@ -1572,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471511</v>
+        <v>471400</v>
       </c>
       <c r="R10" t="n">
-        <v>6796820</v>
+        <v>6797197</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1612,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Måttligt på tallar</t>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133624561</v>
+        <v>133614003</v>
       </c>
       <c r="B11" t="n">
-        <v>79358</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,40 +1650,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471400</v>
+        <v>471474</v>
       </c>
       <c r="R11" t="n">
-        <v>6797197</v>
+        <v>6797013</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1711,14 +1707,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sparsamt på vissa tallar</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,19 +1728,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133624512</v>
       </c>
       <c r="B2" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133614931</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>133614917</v>
       </c>
       <c r="B4" t="n">
-        <v>78362</v>
+        <v>78363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133616224</v>
+        <v>133624485</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,19 +1136,22 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471303</v>
+        <v>471484</v>
       </c>
       <c r="R6" t="n">
-        <v>6796981</v>
+        <v>6797049</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,19 +1178,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt på vissa tallar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,28 +1194,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133624485</v>
+        <v>133616224</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,22 +1242,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Djupån, Djupån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471484</v>
+        <v>471303</v>
       </c>
       <c r="R7" t="n">
-        <v>6797049</v>
+        <v>6796981</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,14 +1281,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt på vissa tallar</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,19 +1302,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
         <v>133613993</v>
       </c>
       <c r="B8" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>133614003</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>133624458</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>133624561</v>
       </c>
       <c r="B11" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133624485</v>
+        <v>133616224</v>
       </c>
       <c r="B6" t="n">
         <v>79359</v>
@@ -1136,22 +1136,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Djupån, Djupån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471484</v>
+        <v>471303</v>
       </c>
       <c r="R6" t="n">
-        <v>6797049</v>
+        <v>6796981</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,14 +1175,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt på vissa tallar</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,26 +1196,25 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133616224</v>
+        <v>133624485</v>
       </c>
       <c r="B7" t="n">
         <v>79359</v>
@@ -1242,19 +1243,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471303</v>
+        <v>471484</v>
       </c>
       <c r="R7" t="n">
-        <v>6796981</v>
+        <v>6797049</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,19 +1285,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt på vissa tallar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,18 +1301,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133614003</v>
+        <v>133624458</v>
       </c>
       <c r="B9" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,37 +1438,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammyren, Dammyren, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471474</v>
+        <v>471511</v>
       </c>
       <c r="R9" t="n">
-        <v>6797013</v>
+        <v>6796820</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,19 +1498,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:59</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,25 +1514,26 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133624458</v>
+        <v>133624561</v>
       </c>
       <c r="B10" t="n">
         <v>79359</v>
@@ -1572,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471511</v>
+        <v>471400</v>
       </c>
       <c r="R10" t="n">
-        <v>6796820</v>
+        <v>6797197</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1612,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Måttligt på tallar</t>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133624561</v>
+        <v>133614003</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,40 +1650,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471400</v>
+        <v>471474</v>
       </c>
       <c r="R11" t="n">
-        <v>6797197</v>
+        <v>6797013</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1711,14 +1707,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sparsamt på vissa tallar</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,19 +1728,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133616224</v>
+        <v>133624485</v>
       </c>
       <c r="B6" t="n">
         <v>79359</v>
@@ -1136,19 +1136,22 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471303</v>
+        <v>471484</v>
       </c>
       <c r="R6" t="n">
-        <v>6796981</v>
+        <v>6797049</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,19 +1178,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt på vissa tallar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,25 +1194,26 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133624485</v>
+        <v>133616224</v>
       </c>
       <c r="B7" t="n">
         <v>79359</v>
@@ -1243,22 +1242,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Djupån, Djupån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471484</v>
+        <v>471303</v>
       </c>
       <c r="R7" t="n">
-        <v>6797049</v>
+        <v>6796981</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,14 +1281,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt på vissa tallar</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,19 +1302,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133624512</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133614931</v>
       </c>
       <c r="B3" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>133614917</v>
       </c>
       <c r="B4" t="n">
-        <v>78363</v>
+        <v>78370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133624485</v>
+        <v>133616224</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,22 +1136,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Djupån, Djupån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471484</v>
+        <v>471303</v>
       </c>
       <c r="R6" t="n">
-        <v>6797049</v>
+        <v>6796981</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,14 +1175,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt på vissa tallar</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,29 +1196,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133616224</v>
+        <v>133624485</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,19 +1243,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471303</v>
+        <v>471484</v>
       </c>
       <c r="R7" t="n">
-        <v>6796981</v>
+        <v>6797049</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,19 +1285,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt på vissa tallar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,18 +1301,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
         <v>133613993</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133614003</v>
+        <v>133624458</v>
       </c>
       <c r="B9" t="n">
-        <v>79117</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,37 +1438,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dammyren, Dammyren, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471474</v>
+        <v>471511</v>
       </c>
       <c r="R9" t="n">
-        <v>6797013</v>
+        <v>6796820</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,19 +1498,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:59</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,28 +1514,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133624458</v>
+        <v>133624561</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471511</v>
+        <v>471400</v>
       </c>
       <c r="R10" t="n">
-        <v>6796820</v>
+        <v>6797197</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1612,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Måttligt på tallar</t>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133624561</v>
+        <v>133614003</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,40 +1650,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471400</v>
+        <v>471474</v>
       </c>
       <c r="R11" t="n">
-        <v>6797197</v>
+        <v>6797013</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1711,14 +1707,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sparsamt på vissa tallar</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,19 +1728,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133624512</v>
+        <v>133616224</v>
       </c>
       <c r="B2" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -704,22 +704,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Djupån, Djupån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471422</v>
+        <v>471303</v>
       </c>
       <c r="R2" t="n">
-        <v>6797163</v>
+        <v>6796981</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,14 +743,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt på tallar</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,67 +764,69 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133614931</v>
+        <v>133624458</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471401</v>
+        <v>471511</v>
       </c>
       <c r="R3" t="n">
-        <v>6797179</v>
+        <v>6796820</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,19 +853,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:32</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,66 +869,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133614917</v>
+        <v>133624485</v>
       </c>
       <c r="B4" t="n">
-        <v>78370</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471401</v>
+        <v>471484</v>
       </c>
       <c r="R4" t="n">
-        <v>6797179</v>
+        <v>6797049</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,19 +959,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:32</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt på vissa tallar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,71 +975,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133615990</v>
+        <v>133624512</v>
       </c>
       <c r="B5" t="n">
-        <v>5181</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471295</v>
+        <v>471422</v>
       </c>
       <c r="R5" t="n">
-        <v>6796999</v>
+        <v>6797163</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,19 +1065,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Måttligt på tallar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,32 +1081,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133616224</v>
+        <v>133624561</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1136,19 +1129,22 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupån, Djupån, Dlr</t>
+          <t>Kangasmäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471303</v>
+        <v>471400</v>
       </c>
       <c r="R6" t="n">
-        <v>6796981</v>
+        <v>6797197</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,19 +1171,14 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:24</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,28 +1187,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133624485</v>
+        <v>133613993</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,40 +1217,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471484</v>
+        <v>471474</v>
       </c>
       <c r="R7" t="n">
-        <v>6797049</v>
+        <v>6797013</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,14 +1274,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tämligen rikligt på vissa tallar</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,29 +1295,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133613993</v>
+        <v>133614591</v>
       </c>
       <c r="B8" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,13 +1348,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471474</v>
+        <v>471466</v>
       </c>
       <c r="R8" t="n">
-        <v>6797013</v>
+        <v>6797059</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1390,7 +1383,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1400,7 +1393,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133624458</v>
+        <v>133614050</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,40 +1431,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471511</v>
+        <v>471466</v>
       </c>
       <c r="R9" t="n">
-        <v>6796820</v>
+        <v>6797059</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,14 +1488,19 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Måttligt på tallar</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,29 +1509,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133624561</v>
+        <v>133614237</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>78377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,40 +1538,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kangasmäck, Dlr</t>
+          <t>Dammyren, Dammyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471400</v>
+        <v>471466</v>
       </c>
       <c r="R10" t="n">
-        <v>6797197</v>
+        <v>6797059</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1604,14 +1595,24 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt på vissa tallar</t>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,29 +1621,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133614003</v>
+        <v>133614917</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>78377</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,34 +1650,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammyren, Dammyren, Dlr</t>
+          <t>Djupån, Djupån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471474</v>
+        <v>471401</v>
       </c>
       <c r="R11" t="n">
-        <v>6797013</v>
+        <v>6797179</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,6 +1743,560 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133614035</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dammyren, Dammyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>471466</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6797059</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133615990</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Djupån, Djupån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>471295</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6796999</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133614003</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dammyren, Dammyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>471474</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6797013</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133614561</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dammyren, Dammyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>471466</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6797059</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133614931</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djupån, Djupån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>471401</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6797179</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21919-2026 artfynd.xlsx
+++ b/artfynd/A 21919-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133616224</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133624458</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133624485</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133624512</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133624561</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133613993</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133614591</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133614050</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133614237</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,6 +1793,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133614917</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133614035</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133615990</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2083,6 +2148,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133614003</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133614561</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,8 +2372,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133614931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>